--- a/项目成员/团队名册.xlsx
+++ b/项目成员/团队名册.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +48,11 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="001A1A2E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="0016213E"/>
       <sz val="10"/>
     </font>
     <font>
@@ -100,7 +105,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -122,11 +127,44 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -138,34 +176,41 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -533,13 +578,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="10.8" customWidth="1" min="2" max="2"/>
     <col width="11.9" customWidth="1" min="3" max="3"/>
-    <col width="32.8" customWidth="1" min="4" max="4"/>
+    <col width="40.5" customWidth="1" min="4" max="4"/>
     <col width="26.2" customWidth="1" min="5" max="5"/>
     <col width="40.5" customWidth="1" min="6" max="6"/>
     <col width="32.8" customWidth="1" min="7" max="7"/>
@@ -555,7 +600,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>版本 v1.3 | 2026-05-23 | 项目总监 阿黑</t>
+          <t>版本 v1.4 | 2026-05-23 | 项目总监 阿黑</t>
         </is>
       </c>
     </row>
@@ -570,276 +615,433 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>用户(创始人) → 阿黑(项目总监) → 腰子(金融专家) | Vega(风控官) | Pulse(数据监理) | Alpha(策略研究员) | Sentinel(宏观巡检)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+          <t>金融团队: 用户(创始人) → 阿黑(项目总监) → 腰子 | Vega | Pulse | Alpha | Sentinel</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>工程团队: 用户(创始人) → 阿黑(项目总监) → Arch | Forge | Dock | Proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>角色</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>召唤</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>核心职责</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>一句话</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>完整定义</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>召唤命令</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>项目总监</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>阿黑</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>调度团队、跟踪全局、主动运营</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>让合适的人做合适的事</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>.claude/agents/项目总监-阿黑.md</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>金融专家</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>腰子</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>/腰子</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>个股分析、策略评估、宏观判断</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>告诉你该不该买</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>.claude/agents/金融专家-腰子.md</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>.claude/commands/腰子.md</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>风控官</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Vega</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>/Vega</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>风险审计、过拟合检测、交易纪律</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>告诉你买了会亏多少</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>.claude/agents/风控官-Vega.md</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>.claude/commands/Vega.md</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>数据监理</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>/Pulse</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>API巡检、缓存审计、数据完整性</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>告诉你数据能不能用</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>.claude/agents/数据监理-Pulse.md</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>.claude/commands/Pulse.md</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>策略研究员</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Alpha</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>/Alpha</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>因子有效性、策略优化、规律挖掘</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>告诉你怎么让策略更聪明</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>.claude/agents/策略研究员-Alpha.md</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>.claude/commands/Alpha.md</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>宏观巡检</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Sentinel</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>/Sentinel</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>政策信号、经济日历、市场情绪</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>告诉你外部环境怎么变</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>.claude/agents/宏观巡检-Sentinel.md</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>.claude/commands/Sentinel.md</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>系统架构师</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Arch</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>/Arch</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>模块设计、技术选型、API契约、重构决策</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>告诉你系统该怎么搭</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>.claude/agents/系统架构师-Arch.md</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>.claude/commands/Arch.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>构建工程师(CI)</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Forge</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>/Forge</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>自动化流水线、定时调度、代码生成</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>让脚本自己跑起来</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>.claude/agents/构建工程师-Forge.md</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>.claude/commands/Forge.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>部署工程师(环境)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Dock</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>/Dock</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>环境配置、依赖管理、版本发布、运行监控</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>让系统跑得稳</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>.claude/agents/部署工程师-Dock.md</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>.claude/commands/Dock.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>质量工程师(测试)</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Proof</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>/Proof</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>测试策略、回归验证、变更影响分析</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>证明改了不会坏</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>.claude/agents/质量工程师-Proof.md</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>.claude/commands/Proof.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -851,7 +1053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -867,121 +1069,189 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>角色</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>详细职能</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>硬边界</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>阿黑 — 项目总监</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>不自己分析，任务是判断什么任务该找谁；复杂任务拆解→分派→综合结论；主动运营：盘前提醒数据巡检、策略退化预警、版本一致性跟踪</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>不自己分析，不越界替角色决策</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>腰子 — 金融专家</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>四维评分：基本面+技术面+资金面+情绪面；策略逻辑评估、宏观环境判断、行业轮动分析；不写代码，分析结论输出给Claude执行</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>不写代码、不编造数据、不预测精确价位</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Vega — 风控官</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>持仓集中度、相关性、流动性、事件风险四位一体；策略过拟合检测、回撤监控、交易纪律审查；红线规则深度审计（不只看格式，审逻辑）；不写代码，只出风险判断</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>不写代码、不提供个股买卖建议</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Pulse — 数据监理</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>三大API（腾讯/新浪/东方财富）连通性巡检；缓存新鲜度审计、数据完整性验证；1+2架构合规检查（主→备→缓存）；不修代码，只给诊断报告和修复指令</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>不修代码，只给诊断报告和修复指令</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Alpha — 策略研究员</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>因子IC/ICIR/分层收益/衰退趋势分析；策略优化提案（权重/阈值/周期）；新因子探索、后评估规律挖掘；不跑代码，设计方案给Claude执行回测</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>不跑代码，设计方案给Claude执行回测</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Sentinel — 宏观巡检</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>每日盘前宏观简报（政策+数据+事件+情绪）；经济日历前瞻（未来一周重要日程预警）；政策信号解读（央行/产业/监管/财政）；事件风险预警（解禁/重大财报/重组审批）；不写代码，只做宏观判断和预警</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>不写代码、不编造政策信息、不提供个股买卖建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Arch — 系统架构师</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>系统模块设计与边界划分、模块间接口契约定义；技术选型评估（Python/PowerShell/调度框架）；数据流设计（API→缓存→评分→报告→交易）；重构决策（识别技术债、判断重构时机）；不写代码，出设计文档和架构图</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>不写代码、不执行部署或运维、不提供金融分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Forge — 构建工程师(CI)</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>CI/CD流水线设计（提交→检查→构建→验证）；自动化调度编排（盘前巡检→数据拉取→评分→报告→交易）；定时任务管理（cron/调度器配置、依赖关系、失败重试策略）；代码生成方案（识别重复模式，设计模板自动生成）；不写代码，出流水线设计和调度方案</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>不写代码、不管理服务器环境、不做架构设计</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Dock — 部署工程师(环境)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>环境配置管理（Python/PowerShell依赖版本锁定、环境隔离）；部署策略设计（灰度发布、回滚方案、发布检查清单）；运行监控方案（健康检查、API可用性监控、异常告警规则）；备份与恢复（数据备份策略、灾备方案、缓存恢复流程）；不写代码，出部署方案和环境诊断</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>不写代码、不设计架构、不构建流水线</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Proof — 质量工程师(测试)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>测试策略设计（单元/集成/回归测试的分层策略）；回归测试用例（评分引擎、数据获取、报告生成的回归验证）；变更影响分析（代码变更前评估影响范围，变更后验证无回归）；代码规范审查（命名/注释/错误处理/日志/API限流合规检查）；不写代码，出测试方案和审查报告</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>不写代码、不修bug、不设计架构或流水线</t>
         </is>
       </c>
     </row>
@@ -999,7 +1269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1021,7 +1291,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Sentinel盘前简报 → Pulse数据巡检 → 腰子选股分析 → Vega风险评估 → Alpha持续优化</t>
         </is>
@@ -1035,141 +1305,178 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>环节</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>角色 · 覆盖内容</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>宏观环境</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Sentinel — 政策信号 / 经济日历 / 市场情绪</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>数据管线</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Pulse — API巡检 / 缓存审计 / 完整性验证</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>分析决策</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>腰子 — 四维评分 / 选股推荐 / 逻辑质疑</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>风险审计</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Vega — 集中度 / 过拟合 / 纪律审查</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>策略进化</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Alpha — 因子IC / 参数优化 / 规律挖掘</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>系统设计</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Arch — 模块划分 / 接口契约 / 技术选型</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>协作纪律</t>
         </is>
       </c>
+      <c r="B14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>分工明确，互不越界</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>腰子不做风控，Vega不挖因子，Alpha不看单票，Sentinel不做个股</t>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>金融：腰子不做风控，Vega不挖因子，Alpha不看单票；工程：Arch不写代码，Forge不管部署，Dock不设计架构，Proof不修bug</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>金融信息流</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Sentinel盘前简报 → Pulse数据巡检 → 腰子选股分析 → Vega风险评估 → Alpha持续优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>工程信息流</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Arch系统设计 → Forge构建流水线 → Dock部署上线 → Proof质量验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>跨团队协作</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>金融团队提需求 → 工程团队设计方案并实施 → 金融团队验证结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>争议解决</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>角色间有分歧时，阿黑做最终判断，用户做最终决策</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>版本追踪</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>每个角色定义文件独立版本管理</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>红线共守</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>所有角色共同遵守规则红线最新版本</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>信息流顺序</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>盘前简报→数据巡检→选股分析→风险评估→策略优化</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1498,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19.6" customWidth="1" min="1" max="1"/>
     <col width="44.90000000000001" customWidth="1" min="2" max="2"/>
-    <col width="21.8" customWidth="1" min="3" max="3"/>
+    <col width="28.4" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1208,187 +1515,272 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>路径</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>本名册(.md)</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>项目成员/团队名册.md</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Markdown 源文件</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>本名册(.xlsx)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>项目成员/团队名册.xlsx</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Excel 版本（本文件）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>阿黑角色定义</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>.claude/agents/项目总监-阿黑.md</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>项目总监完整人设</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>腰子角色定义</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>.claude/agents/金融专家-腰子.md</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>金融专家完整人设</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Vega角色定义</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>.claude/agents/风控官-Vega.md</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>风控官完整人设</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Pulse角色定义</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>.claude/agents/数据监理-Pulse.md</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>数据监理完整人设</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Alpha角色定义</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>.claude/agents/策略研究员-Alpha.md</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>策略研究员完整人设</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Sentinel角色定义</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>.claude/agents/宏观巡检-Sentinel.md</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>宏观巡检完整人设</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>召唤命令 ×5</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Arch角色定义</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>.claude/agents/系统架构师-Arch.md</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>系统架构师完整人设</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Forge角色定义</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>.claude/agents/构建工程师-Forge.md</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>构建工程师(CI)完整人设</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Dock角色定义</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>.claude/agents/部署工程师-Dock.md</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>部署工程师(环境)完整人设</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Proof角色定义</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>.claude/agents/质量工程师-Proof.md</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>质量工程师(测试)完整人设</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>召唤命令 ×9</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>.claude/commands/腰子.md 等</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>角色召唤触发器</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>名册生成工具</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>代码文件/tools/generate_roster_xlsx.py</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>自动生成团队名册.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>规则红线</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>规则红线/分析的规则红线--Claude_v1.7.md</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>规则红线/分析的规则红线--Claude_v1.8.md</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>项目最高优先级规则</t>
         </is>
